--- a/MOO_dumb.xlsx
+++ b/MOO_dumb.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,37 +612,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.169623636098072</v>
+        <v>3.211727764227911</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7686018097107108</v>
+        <v>35.69980051350196</v>
       </c>
       <c r="C2" t="n">
-        <v>0.724881382759484</v>
+        <v>49.32313571854721</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5609165741995512</v>
+        <v>7.194393870009577</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7120267743692991</v>
+        <v>2.087345026321207</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9184080820754739</v>
+        <v>0.4046279306950412</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9999999999999991</v>
+        <v>40.99050977600787</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07516789507882964</v>
+        <v>20.38806373245946</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5069148185094834</v>
+        <v>12.54833652260955</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5455151489076497</v>
+        <v>1004.790169772464</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5444379964649166</v>
+        <v>0.3284275702257617</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -681,28 +681,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -714,10 +714,450 @@
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>2998.024191691884</v>
+        <v>29.59142356167187</v>
       </c>
       <c r="AJ2" t="n">
-        <v>919.843890974429</v>
+        <v>15.41095366705932</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3.514931418442879</v>
+      </c>
+      <c r="B3" t="n">
+        <v>34.07418630114182</v>
+      </c>
+      <c r="C3" t="n">
+        <v>49.3231357196766</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.194394780198646</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.087352944660894</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4046369205766448</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40.9905098534721</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15.66264333133755</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12.62952938478339</v>
+      </c>
+      <c r="J3" t="n">
+        <v>919.468728618501</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.3375553206203771</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>45.25446356782789</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>18.07722397572782</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3.514198905819227</v>
+      </c>
+      <c r="B4" t="n">
+        <v>35.20880708060687</v>
+      </c>
+      <c r="C4" t="n">
+        <v>49.3231357196766</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.194393908022482</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.087352409970195</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4046257684089247</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40.99050977603033</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20.14287297240833</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.371213341008394</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1009.137346653863</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.3568431617928581</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>37.12115219164844</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>15.45290821389691</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3.51419885355706</v>
+      </c>
+      <c r="B5" t="n">
+        <v>34.07964273712333</v>
+      </c>
+      <c r="C5" t="n">
+        <v>49.3231357196766</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.1943939080018</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.087346518728851</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4046258728491872</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40.99050977600787</v>
+      </c>
+      <c r="H5" t="n">
+        <v>17.17712986274855</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.440035139805517</v>
+      </c>
+      <c r="J5" t="n">
+        <v>976.4666984696005</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.3580760565723303</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>44.92646806473551</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>15.9136501931641</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1.989275377792233</v>
+      </c>
+      <c r="B6" t="n">
+        <v>35.20593789805081</v>
+      </c>
+      <c r="C6" t="n">
+        <v>49.32313571965253</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.194394979595189</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.087345030180211</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4046257721571021</v>
+      </c>
+      <c r="G6" t="n">
+        <v>40.99050977600787</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20.38954434068695</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12.36983998079178</v>
+      </c>
+      <c r="J6" t="n">
+        <v>958.4629579111569</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3577956464737698</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>23.2024426493971</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>14.14765221733798</v>
       </c>
     </row>
   </sheetData>
